--- a/output/graficos_dimensiones/comunal_p_aps_a_2019_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_p_aps_a_2019_biobio.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 20:38</t>
+    <t xml:space="preserve">2026-09-09 23:36</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_p_aps_a_2019_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_p_aps_a_2019_biobio.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 23:36</t>
+    <t xml:space="preserve">2026-09-18 10:25</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_p_aps_a_2019_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_p_aps_a_2019_biobio.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 10:25</t>
+    <t xml:space="preserve">2026-09-23 12:58</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_p_aps_a_2019_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_p_aps_a_2019_biobio.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 12:58</t>
+    <t xml:space="preserve">2026-10-02 15:02</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_p_aps_a_2019_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_p_aps_a_2019_biobio.xlsx
@@ -51,7 +51,7 @@
     <t xml:space="preserve">Lota</t>
   </si>
   <si>
-    <t xml:space="preserve">Los Alamos</t>
+    <t xml:space="preserve">Los Álamos</t>
   </si>
   <si>
     <t xml:space="preserve">Penco</t>
@@ -93,7 +93,7 @@
     <t xml:space="preserve">Florida</t>
   </si>
   <si>
-    <t xml:space="preserve">Los Angeles</t>
+    <t xml:space="preserve">Los Ángeles</t>
   </si>
   <si>
     <t xml:space="preserve">Chiguayante</t>
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 15:02</t>
+    <t xml:space="preserve">2026-10-04 09:39</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_p_aps_a_2019_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_p_aps_a_2019_biobio.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-04 09:39</t>
+    <t xml:space="preserve">2026-10-05 13:07</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
